--- a/checklists/[day].xlsx
+++ b/checklists/[day].xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karst\Documents\GitHub\classroom-notes\checklists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161BE296-8F00-4549-BC53-68CE47151505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61668617-08B5-42CA-9F9A-3B30B57762BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1400,7 +1400,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0F66A8-1D07-42AD-AE60-F9228E214003}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1447,7 +1446,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>86</v>
       </c>
@@ -1471,7 +1470,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>114</v>
       </c>
@@ -1495,7 +1494,7 @@
       </c>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>87</v>
       </c>
@@ -1531,6 +1530,9 @@
       <c r="B5" t="s">
         <v>127</v>
       </c>
+      <c r="C5">
+        <v>249617</v>
+      </c>
       <c r="D5" s="5" t="s">
         <v>104</v>
       </c>
@@ -1550,7 +1552,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>122</v>
       </c>
@@ -1579,7 +1581,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>68</v>
       </c>
@@ -1602,7 +1604,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -1628,7 +1630,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>137</v>
       </c>
@@ -1660,7 +1662,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -1692,7 +1694,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>90</v>
       </c>
@@ -1718,7 +1720,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>84</v>
       </c>
@@ -1741,7 +1743,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -1761,7 +1763,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>63</v>
       </c>
@@ -1819,7 +1821,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>89</v>
       </c>
@@ -1915,7 +1917,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -1973,7 +1975,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>111</v>
       </c>
@@ -1999,7 +2001,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -2086,7 +2088,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>65</v>
       </c>
@@ -2120,11 +2122,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J25" xr:uid="{8B0F66A8-1D07-42AD-AE60-F9228E214003}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="10:45"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
       <sortCondition ref="B1:B25"/>
     </sortState>
